--- a/IPC_Regiones.xlsx
+++ b/IPC_Regiones.xlsx
@@ -430,7 +430,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>0.34</v>
+        <v>0.3400000000000001</v>
       </c>
       <c r="C2" s="2">
         <v>114.1536619704414</v>
@@ -447,7 +447,7 @@
         <v>0.3100000000000001</v>
       </c>
       <c r="C3" s="2">
-        <v>113.9695049132316</v>
+        <v>113.9695049132317</v>
       </c>
       <c r="D3" s="2">
         <v>0.31</v>
@@ -461,10 +461,10 @@
         <v>0.04999999999999998</v>
       </c>
       <c r="C4" s="2">
-        <v>114.4214389723145</v>
+        <v>114.4214389723144</v>
       </c>
       <c r="D4" s="2">
-        <v>0.04999999999999996</v>
+        <v>0.04999999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -486,13 +486,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>0.07000000000000005</v>
+        <v>0.07000000000000003</v>
       </c>
       <c r="C6" s="2">
-        <v>115.0525567002664</v>
+        <v>115.0525567002663</v>
       </c>
       <c r="D6" s="2">
-        <v>0.07000000000000003</v>
+        <v>0.07000000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -500,10 +500,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>0.06000000000000005</v>
+        <v>0.06000000000000004</v>
       </c>
       <c r="C7" s="2">
-        <v>114.2055239750955</v>
+        <v>114.2055239750954</v>
       </c>
       <c r="D7" s="2">
         <v>0.06000000000000003</v>
